--- a/templates/TAMHA_Team_Budget_Master_Template.xlsx
+++ b/templates/TAMHA_Team_Budget_Master_Template.xlsx
@@ -634,9 +634,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Truro Bearcats U13 A</t>
+          <t>[Enter Team Name - e.g., Truro Bearcats U13 A]</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Tom Malone</t>
+          <t>[Head Coach Full Name]</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Matt Redmond</t>
+          <t>[Team Manager Full Name]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Amy Redmond</t>
+          <t>[Team Treasurer Full Name]</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>299688400</t>
+          <t>[Enter 9-Digit Account #]</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Initial Budget (Oct 30)</t>
+          <t>Preliminary Budget (Oct 30)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Major Corporate Sponsor (e.g. Jersey / Gold)</t>
+          <t>[Major Team Sponsor - e.g. Local Business]</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -1642,30 +1642,30 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Local Business Owner</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>E-transfer</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Banner Sponsor 1 (Gold)</t>
+          <t>[Gold Banner Sponsor 1]</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -1675,30 +1675,30 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Business Contact</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
         <v>500</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Banner Sponsor 2 (Gold)</t>
+          <t>[Gold Banner Sponsor 2]</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -1708,30 +1708,30 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Business Contact</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
         <v>500</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Banner Sponsor 3 (Silver)</t>
+          <t>[Silver Banner Sponsor 1]</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -1741,30 +1741,30 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Business Contact</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
         <v>250</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Banner Sponsor 4 (Silver)</t>
+          <t>[Silver Banner Sponsor 2]</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -1774,30 +1774,30 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Business Contact</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>E-transfer</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E10" s="11" t="n">
         <v>250</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Banner Sponsor 5 (Silver)</t>
+          <t>[Silver Banner Sponsor 3]</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -1807,30 +1807,30 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Business Contact</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
         <v>250</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Banner Sponsor 6 (Bronze)</t>
+          <t>[Bronze Banner Sponsor 1]</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -1840,30 +1840,30 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Business Contact</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E12" s="11" t="n">
         <v>100</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Banner Sponsor 7 (Bronze)</t>
+          <t>[Bronze Banner Sponsor 2]</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -1873,23 +1873,23 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Business Contact</t>
+          <t>[Contact Name]</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>E-transfer</t>
+          <t>[Cheque / E-transfer]</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
         <v>100</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1959,24 +1959,24 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Team Bottle Drive (Fall)</t>
+          <t>[Team Bottle Drive - Fall]</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Oct 19, 2026</t>
+          <t>[Oct 2026]</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Parent Volunteer</t>
+          <t>[Parent Volunteer]</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>1368</v>
+        <v>0</v>
       </c>
       <c r="F18" s="11">
         <f>E18-D18</f>
@@ -1984,31 +1984,31 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Completed - Deposited</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Pot O' Gold 50/50 Raffle</t>
+          <t>[50/50 Raffle - e.g. Pot O' Gold]</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Nov 15, 2026</t>
+          <t>[Nov 2026]</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Treasurer</t>
+          <t>[Treasurer]</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
       <c r="F19" s="11">
         <f>E19-D19</f>
@@ -2016,31 +2016,31 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Completed - Net after prize</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Grand In Your Hand / Cash Draw</t>
+          <t>[Ticket Draw / Grand In Your Hand]</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Dec 10, 2026</t>
+          <t>[Dec 2026]</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>Team Manager</t>
+          <t>[Manager]</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="11">
         <f>E20-D20</f>
@@ -2048,28 +2048,28 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Super Bowl Square Board / Silent Auction</t>
+          <t>[Square Board / Silent Auction]</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Feb 7, 2027</t>
+          <t>[Feb 2027]</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Parent Committee</t>
+          <t>[Parent Committee]</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>0</v>
@@ -2080,24 +2080,24 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Planned for Winter</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Optional Team Fundraiser 5</t>
+          <t>[Optional Fundraiser 5]</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>[TBD]</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>[Volunteer]</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Contingency</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
         <v/>
       </c>
       <c r="E27" s="11" t="n">
-        <v>3850</v>
+        <v>0</v>
       </c>
       <c r="F27" s="11">
         <f>E27-D27</f>
@@ -2230,7 +2230,7 @@
         <v/>
       </c>
       <c r="E28" s="11" t="n">
-        <v>3850</v>
+        <v>0</v>
       </c>
       <c r="F28" s="11">
         <f>E28-D28</f>
@@ -2260,7 +2260,7 @@
         <v/>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="F29" s="11">
         <f>E29-D29</f>
@@ -2386,7 +2386,7 @@
         <v/>
       </c>
       <c r="E37" s="11" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v/>
       </c>
       <c r="G49" s="28">
-        <f>IF(F49&gt;=0,"Surplus / Target Met","Deficit")</f>
+        <f>IF(F49&gt;=0,"Surplus / Target Met","Pending")</f>
         <v/>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
         <v>3850</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>3850</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>3850</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3850</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>550</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1032.29</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Tournament 1: Early Bird / Challenge Cup</t>
+          <t>Tournament 1: [Early Bird / Pre-Season Event]</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Amherst, NS</t>
+          <t>[Host Town, NS]</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -2870,7 +2870,7 @@
         <v>850</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Tournament 2: Holiday / New Year Invitational</t>
+          <t>Tournament 2: [Holiday / Winter Invitational]</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Local / Regional</t>
+          <t>[Host Town, NS]</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -2903,7 +2903,7 @@
         <v>900</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>867</v>
+        <v>0</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Tournament 3: SEDMHA Tournament</t>
+          <t>Tournament 3: [SEDMHA / March Tournament]</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1325</v>
+        <v>1200</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1325</v>
+        <v>0</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Tournament 4: Away / Friendship Tournament</t>
+          <t>Tournament 4: [Away / Travel Tournament]</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>PEI / New Brunswick</t>
+          <t>[PEI / NB / Local]</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -2969,7 +2969,7 @@
         <v>850</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -3056,23 +3056,23 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>RECC / West Colchester</t>
+          <t>Local Rink / RECC</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Pre-Season / Mid-Season</t>
+          <t>Pre-Season / Practice</t>
         </is>
       </c>
       <c r="E28" s="11" t="n">
         <v>990</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Extra development sessions</t>
+          <t>Extra team development ice</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>RECC Truro</t>
+          <t>Home Rink</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -3101,11 +3101,11 @@
         <v>516</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Home exhibition games</t>
+          <t>Home exhibition game slots</t>
         </is>
       </c>
     </row>
@@ -3134,11 +3134,11 @@
         <v>180</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>2 refs + linesmen</t>
+          <t>Cash payout for officials</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Truro Timekeepers</t>
+          <t>Timekeeper Association</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -3167,11 +3167,11 @@
         <v>60</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Electronic game sheet / clock</t>
+          <t>Clock / game sheet operator</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         <v>550</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Retractable / Arena Banner</t>
+          <t>Arena Display Banner</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>200</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>168.59</v>
+        <v>0</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>250</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>245.59</v>
+        <v>0</v>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>680</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
@@ -3431,11 +3431,11 @@
         <v>120</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Team equipment</t>
+          <t>Team practice equipment</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
         <v>450</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>473.51</v>
+        <v>0</v>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>500</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>250</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>282.85</v>
+        <v>0</v>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Head Coach &amp; 3 Assistants</t>
+          <t>Head Coach &amp; Bench Staff</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -3629,7 +3629,7 @@
         <v>150</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>105</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>45</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>October 31, 2026</t>
+          <t>[Enter Statement Date - e.g. Oct 31, 2026]</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
-        <v>10302.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4086,90 +4086,90 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Sponsorship Cheque - Gold Banner</t>
+          <t>[Deposit 1 Description]</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Oct 28, 2026</t>
+          <t>[Date]</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Local Business</t>
+          <t>[Source / Payer]</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>[Method]</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Deposited via mobile, clearing</t>
+          <t>[Pending clearance]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Late Parent Rep Fee Installment</t>
+          <t>[Deposit 2 Description]</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Oct 30, 2026</t>
+          <t>[Date]</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Parent Name</t>
+          <t>[Source / Payer]</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>E-transfer</t>
+          <t>[Method]</t>
         </is>
       </c>
       <c r="E12" s="11" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Pending deposit acceptance</t>
+          <t>[Pending clearance]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Bottle Drive Cash Deposit</t>
+          <t>[Deposit 3 Description]</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Oct 31, 2026</t>
+          <t>[Date]</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>[Source / Payer]</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>[Method]</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Night deposit box</t>
+          <t>[Pending clearance]</t>
         </is>
       </c>
     </row>
@@ -4250,26 +4250,26 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Cheque #101</t>
+          <t>[Cheque #101]</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>[Date]</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Amherst Minor Hockey</t>
+          <t>[Payee / Vendor]</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Tournament Entry Fee</t>
+          <t>[Description / Purpose]</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
@@ -4280,60 +4280,60 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Cheque #102</t>
+          <t>[Cheque #102]</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Oct 20, 2026</t>
+          <t>[Date]</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Local Print Shop</t>
+          <t>[Payee / Vendor]</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Sponsor Banner Printing</t>
+          <t>[Description / Purpose]</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>168.59</v>
+        <v>0</v>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Issued, in mail</t>
+          <t>Issued, not yet cashed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Cheque #103</t>
+          <t>[Cheque #103]</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Oct 25, 2026</t>
+          <t>[Date]</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Apparel Vendor</t>
+          <t>[Payee / Vendor]</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Practice Jerseys Deposit</t>
+          <t>[Description / Purpose]</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Issued</t>
+          <t>Issued, not yet cashed</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -4541,35 +4541,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>1</v>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>#01</t>
+        </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Player 1 Name</t>
+          <t>[Player 01 Legal Name]</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 1</t>
+          <t>[Parent / Guardian of Player 01]</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>parent1@example.com</t>
+          <t>[parent01@example.com]</t>
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F5" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G5" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H5" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="36">
         <f>SUM(E5:H5)</f>
@@ -4581,40 +4583,42 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>#02</t>
+        </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Player 2 Name</t>
+          <t>[Player 02 Legal Name]</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 2</t>
+          <t>[Parent / Guardian of Player 02]</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>parent2@example.com</t>
+          <t>[parent02@example.com]</t>
         </is>
       </c>
       <c r="E6" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="36">
         <f>SUM(E6:H6)</f>
@@ -4626,40 +4630,42 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>3</v>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>#03</t>
+        </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Player 3 Name</t>
+          <t>[Player 03 Legal Name]</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 3</t>
+          <t>[Parent / Guardian of Player 03]</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>parent3@example.com</t>
+          <t>[parent03@example.com]</t>
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="36">
         <f>SUM(E7:H7)</f>
@@ -4671,40 +4677,42 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>#04</t>
+        </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Player 4 Name</t>
+          <t>[Player 04 Legal Name]</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 4</t>
+          <t>[Parent / Guardian of Player 04]</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>parent4@example.com</t>
+          <t>[parent04@example.com]</t>
         </is>
       </c>
       <c r="E8" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="36">
         <f>SUM(E8:H8)</f>
@@ -4716,40 +4724,42 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>5</v>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>#05</t>
+        </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Player 5 Name</t>
+          <t>[Player 05 Legal Name]</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 5</t>
+          <t>[Parent / Guardian of Player 05]</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>parent5@example.com</t>
+          <t>[parent05@example.com]</t>
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="36">
         <f>SUM(E9:H9)</f>
@@ -4761,40 +4771,42 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>#06</t>
+        </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Player 6 Name</t>
+          <t>[Player 06 Legal Name]</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 6</t>
+          <t>[Parent / Guardian of Player 06]</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>parent6@example.com</t>
+          <t>[parent06@example.com]</t>
         </is>
       </c>
       <c r="E10" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="36">
         <f>SUM(E10:H10)</f>
@@ -4806,40 +4818,42 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
-        <v>7</v>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>#07</t>
+        </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Player 7 Name</t>
+          <t>[Player 07 Legal Name]</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 7</t>
+          <t>[Parent / Guardian of Player 07]</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>parent7@example.com</t>
+          <t>[parent07@example.com]</t>
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="36">
         <f>SUM(E11:H11)</f>
@@ -4851,40 +4865,42 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>#08</t>
+        </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Player 8 Name</t>
+          <t>[Player 08 Legal Name]</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 8</t>
+          <t>[Parent / Guardian of Player 08]</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>parent8@example.com</t>
+          <t>[parent08@example.com]</t>
         </is>
       </c>
       <c r="E12" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="36">
         <f>SUM(E12:H12)</f>
@@ -4896,40 +4912,42 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>9</v>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>#09</t>
+        </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Player 9 Name</t>
+          <t>[Player 09 Legal Name]</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 9</t>
+          <t>[Parent / Guardian of Player 09]</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>parent9@example.com</t>
+          <t>[parent09@example.com]</t>
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="36">
         <f>SUM(E13:H13)</f>
@@ -4941,40 +4959,42 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Player 10 Name</t>
+          <t>[Player 10 Legal Name]</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 10</t>
+          <t>[Parent / Guardian of Player 10]</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>parent10@example.com</t>
+          <t>[parent10@example.com]</t>
         </is>
       </c>
       <c r="E14" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="36">
         <f>SUM(E14:H14)</f>
@@ -4986,40 +5006,42 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n">
-        <v>11</v>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Player 11 Name</t>
+          <t>[Player 11 Legal Name]</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 11</t>
+          <t>[Parent / Guardian of Player 11]</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>parent11@example.com</t>
+          <t>[parent11@example.com]</t>
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="36">
         <f>SUM(E15:H15)</f>
@@ -5031,40 +5053,42 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Player 12 Name</t>
+          <t>[Player 12 Legal Name]</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 12</t>
+          <t>[Parent / Guardian of Player 12]</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>parent12@example.com</t>
+          <t>[parent12@example.com]</t>
         </is>
       </c>
       <c r="E16" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="36">
         <f>SUM(E16:H16)</f>
@@ -5076,40 +5100,42 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="n">
-        <v>13</v>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Player 13 Name</t>
+          <t>[Player 13 Legal Name]</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 13</t>
+          <t>[Parent / Guardian of Player 13]</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>parent13@example.com</t>
+          <t>[parent13@example.com]</t>
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="36">
         <f>SUM(E17:H17)</f>
@@ -5121,40 +5147,42 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n">
-        <v>14</v>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Player 14 Name</t>
+          <t>[Player 14 Legal Name]</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 14</t>
+          <t>[Parent / Guardian of Player 14]</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>parent14@example.com</t>
+          <t>[parent14@example.com]</t>
         </is>
       </c>
       <c r="E18" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="36">
         <f>SUM(E18:H18)</f>
@@ -5166,40 +5194,42 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="n">
-        <v>15</v>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Player 15 Name</t>
+          <t>[Player 15 Legal Name]</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 15</t>
+          <t>[Parent / Guardian of Player 15]</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>parent15@example.com</t>
+          <t>[parent15@example.com]</t>
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="36">
         <f>SUM(E19:H19)</f>
@@ -5211,40 +5241,42 @@
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="n">
-        <v>16</v>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>#16</t>
+        </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Player 16 Name</t>
+          <t>[Player 16 Legal Name]</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 16</t>
+          <t>[Parent / Guardian of Player 16]</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>parent16@example.com</t>
+          <t>[parent16@example.com]</t>
         </is>
       </c>
       <c r="E20" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="36">
         <f>SUM(E20:H20)</f>
@@ -5256,40 +5288,42 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="n">
-        <v>17</v>
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>#17</t>
+        </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Player 17 Name</t>
+          <t>[Player 17 Legal Name]</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Parent of Player 17</t>
+          <t>[Parent / Guardian of Player 17]</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>parent17@example.com</t>
+          <t>[parent17@example.com]</t>
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>226.47</v>
+        <v>0</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="36">
         <f>SUM(E21:H21)</f>
@@ -5301,7 +5335,7 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>Cheque on File</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/templates/TAMHA_Team_Budget_Master_Template.xlsx
+++ b/templates/TAMHA_Team_Budget_Master_Template.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <i val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -68,7 +75,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +98,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F0F9FF"/>
         <bgColor rgb="00F0F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,7 +131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -138,6 +151,20 @@
       </top>
       <bottom style="thin">
         <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="003B82F6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
       </bottom>
     </border>
     <border>
@@ -172,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,16 +212,20 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,24 +240,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,28 +272,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -682,8 +716,9 @@
           <t>Roster Players:</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>17</v>
+      <c r="G4" s="5">
+        <f>IF(COUNTA('Roster &amp; Fee Tracker'!B5:B25)&gt;0, COUNTA('Roster &amp; Fee Tracker'!B5:B25), 17)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -750,803 +785,837 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ℹ️ MANAGER INSTRUCTIONS: Do NOT manually type budget figures into this summary tab! All numbers roll up automatically from the detailed line items entered on the 'Income' and 'Expenses' tabs. Simply enter your team's budget line items on those two tabs.
+• Rep Teams: Rep fees are $9,500 total ($4,750 per installment; includes mandatory sweater/jersey fund). AAA teams are $11,500. C/House teams pay $0.
+• Optional Tools: Both the 'Bank Rec' and 'Roster &amp; Fee Tracker' tabs are optional team management tools and are NOT required for your budget submission.</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>1.0 REVENUE SUMMARY (ROLLUP FROM INCOME SHEET)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Revenue Category</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Actual YTD ($)</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Variance ($)</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>% Achieved</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Notes / Verification</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>1.1 Corporate &amp; Local Sponsorships</t>
         </is>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="13">
         <f>Income!E14</f>
         <v/>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="13">
         <f>Income!F14</f>
         <v/>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="13">
         <f>C14-B14</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="14">
         <f>IF(B14&gt;0, C14/B14, 0)</f>
         <v/>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <f>IF(D14&gt;=0,"On Target","Pending")</f>
         <v/>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Team sponsors &amp; banner ads</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>1.2 Team Fundraising Initiatives</t>
         </is>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="13">
         <f>Income!D23</f>
         <v/>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="13">
         <f>Income!E23</f>
         <v/>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="13">
         <f>C15-B15</f>
         <v/>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="14">
         <f>IF(B15&gt;0, C15/B15, 0)</f>
         <v/>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="15">
         <f>IF(D15&gt;=0,"On Target","In Progress")</f>
         <v/>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Bottle drive, 50/50, draws</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>1.3 Parent Fee Contributions (Rep/Team Fees)</t>
         </is>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="13">
         <f>Income!D33</f>
         <v/>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="13">
         <f>Income!E33</f>
         <v/>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="13">
         <f>C16-B16</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="14">
         <f>IF(B16&gt;0, C16/B16, 0)</f>
         <v/>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="15">
         <f>IF(D16&gt;=0,"Collected","Pending")</f>
         <v/>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Per-player installments</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>1.4 Parent Jersey Deposits (Held in Trust)</t>
         </is>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="13">
         <f>Income!D41</f>
         <v/>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="13">
         <f>Income!E41</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="13">
         <f>C17-B17</f>
         <v/>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="14">
         <f>IF(B17&gt;0, C17/B17, 0)</f>
         <v/>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="15">
         <f>IF(D17&gt;=0,"Collected","Pending")</f>
         <v/>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Refunded at end of season</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>1.5 Bank Interest &amp; Miscellaneous Revenue</t>
         </is>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="13">
         <f>Income!D47</f>
         <v/>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="13">
         <f>Income!E47</f>
         <v/>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="13">
         <f>C18-B18</f>
         <v/>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="14">
         <f>IF(B18&gt;0, C18/B18, 0)</f>
         <v/>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>"Balanced"</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Account interest / other</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>TOTAL PROJECTED &amp; ACTUAL REVENUE</t>
         </is>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="17">
         <f>SUM(B14:B18)</f>
         <v/>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="17">
         <f>SUM(C14:C18)</f>
         <v/>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="17">
         <f>C21-B21</f>
         <v/>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="18">
         <f>IF(B21&gt;0, C21/B21, 0)</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="19">
         <f>IF(D21&gt;=0,"SURPLUS / ON TRACK","DEFICIT")</f>
         <v/>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>Rolls up all 5 income categories</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>2.0 EXPENSE SUMMARY (ROLLUP FROM EXPENSES SHEET)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Expense Category</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Actual YTD ($)</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Variance ($)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>% Spent</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Notes / Verification</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>2.1 TAMHA Association &amp; League Fees</t>
         </is>
       </c>
-      <c r="B26" s="11">
-        <f>Expenses!E14</f>
-        <v/>
-      </c>
-      <c r="C26" s="11">
-        <f>Expenses!F14</f>
-        <v/>
-      </c>
-      <c r="D26" s="11">
+      <c r="B26" s="13">
+        <f>Expenses!E11</f>
+        <v/>
+      </c>
+      <c r="C26" s="13">
+        <f>Expenses!F11</f>
+        <v/>
+      </c>
+      <c r="D26" s="13">
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="14">
         <f>IF(B26&gt;0, C26/B26, 0)</f>
         <v/>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="15">
         <f>IF(C26&lt;=B26,"On Budget","Over")</f>
         <v/>
       </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Rep fees ($7,700), sweater fund ($550)</t>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Rep fees ($9,500 total; includes jersey fund)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>2.2 Tournaments &amp; Jamborees Entry Fees</t>
         </is>
       </c>
-      <c r="B27" s="11">
-        <f>Expenses!E24</f>
-        <v/>
-      </c>
-      <c r="C27" s="11">
-        <f>Expenses!F24</f>
-        <v/>
-      </c>
-      <c r="D27" s="11">
+      <c r="B27" s="13">
+        <f>Expenses!E22</f>
+        <v/>
+      </c>
+      <c r="C27" s="13">
+        <f>Expenses!F22</f>
+        <v/>
+      </c>
+      <c r="D27" s="13">
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="14">
         <f>IF(B27&gt;0, C27/B27, 0)</f>
         <v/>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="15">
         <f>IF(C27&lt;=B27,"On Budget","Over")</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Tournament registrations</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>2.3 Extra Practice Ice &amp; Game Officials</t>
         </is>
       </c>
-      <c r="B28" s="11">
-        <f>Expenses!E33</f>
-        <v/>
-      </c>
-      <c r="C28" s="11">
-        <f>Expenses!F33</f>
-        <v/>
-      </c>
-      <c r="D28" s="11">
+      <c r="B28" s="13">
+        <f>Expenses!E32</f>
+        <v/>
+      </c>
+      <c r="C28" s="13">
+        <f>Expenses!F32</f>
+        <v/>
+      </c>
+      <c r="D28" s="13">
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="14">
         <f>IF(B28&gt;0, C28/B28, 0)</f>
         <v/>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="15">
         <f>IF(C28&lt;=B28,"On Budget","Over")</f>
         <v/>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Ice rental, ref &amp; timekeeper fees</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>2.4 Team Apparel, Items &amp; Equipment</t>
         </is>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="13">
         <f>Expenses!E43</f>
         <v/>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="13">
         <f>Expenses!F43</f>
         <v/>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="13">
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="14">
         <f>IF(B29&gt;0, C29/B29, 0)</f>
         <v/>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="15">
         <f>IF(C29&lt;=B29,"On Budget","Over")</f>
         <v/>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Practice jerseys, banner, name bars, socks</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>2.5 Team Events &amp; Player Activities</t>
         </is>
       </c>
-      <c r="B30" s="11">
-        <f>Expenses!E52</f>
-        <v/>
-      </c>
-      <c r="C30" s="11">
-        <f>Expenses!F52</f>
-        <v/>
-      </c>
-      <c r="D30" s="11">
+      <c r="B30" s="13">
+        <f>Expenses!E51</f>
+        <v/>
+      </c>
+      <c r="C30" s="13">
+        <f>Expenses!F51</f>
+        <v/>
+      </c>
+      <c r="D30" s="13">
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="14">
         <f>IF(B30&gt;0, C30/B30, 0)</f>
         <v/>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="15">
         <f>IF(C30&lt;=B30,"On Budget","Over")</f>
         <v/>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Holiday party, year-end banquet, gifts</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>2.6 Operating Costs, Banking &amp; Contingency</t>
         </is>
       </c>
-      <c r="B31" s="11">
-        <f>Expenses!E60</f>
-        <v/>
-      </c>
-      <c r="C31" s="11">
-        <f>Expenses!F60</f>
-        <v/>
-      </c>
-      <c r="D31" s="11">
+      <c r="B31" s="13">
+        <f>Expenses!E59</f>
+        <v/>
+      </c>
+      <c r="C31" s="13">
+        <f>Expenses!F59</f>
+        <v/>
+      </c>
+      <c r="D31" s="13">
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="14">
         <f>IF(B31&gt;0, C31/B31, 0)</f>
         <v/>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="15">
         <f>IF(C31&lt;=B31,"On Budget","Over")</f>
         <v/>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Mosaik fees, cheques, contingency buffer</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>2.7 Return of Parent Jersey Deposits</t>
         </is>
       </c>
-      <c r="B32" s="11">
-        <f>Expenses!E66</f>
-        <v/>
-      </c>
-      <c r="C32" s="11">
-        <f>Expenses!F66</f>
-        <v/>
-      </c>
-      <c r="D32" s="11">
+      <c r="B32" s="13">
+        <f>Expenses!E65</f>
+        <v/>
+      </c>
+      <c r="C32" s="13">
+        <f>Expenses!F65</f>
+        <v/>
+      </c>
+      <c r="D32" s="13">
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="14">
         <f>IF(B32&gt;0, C32/B32, 0)</f>
         <v/>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="15">
         <f>IF(C32&lt;=B32,"Pending EOY","Refunded")</f>
         <v/>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Refunded to parents upon jersey return</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>TOTAL PROJECTED &amp; ACTUAL EXPENSES</t>
         </is>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="17">
         <f>SUM(B26:B32)</f>
         <v/>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="17">
         <f>SUM(C26:C32)</f>
         <v/>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="17">
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="18">
         <f>IF(B36&gt;0, C36/B36, 0)</f>
         <v/>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>IF(D36&gt;=0,"UNDER BUDGET","OVER BUDGET")</f>
         <v/>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>Rolls up all 7 expense categories</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>3.0 NET POSITION &amp; PER-PLAYER BREAKDOWN</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Net Team Cash Position (Revenue - Expenses)</t>
         </is>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="22">
         <f>B21-B36</f>
         <v/>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="22">
         <f>C21-C36</f>
         <v/>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="22">
         <f>C39-B39</f>
         <v/>
       </c>
-      <c r="E39" s="19" t="inlineStr"/>
-      <c r="F39" s="21">
+      <c r="E39" s="21" t="inlineStr"/>
+      <c r="F39" s="23">
         <f>IF(B39&gt;=0,"BALANCED / SURPLUS","DEFICIT")</f>
         <v/>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>Target is balanced ($0.00)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Gross Team Operating Cost Per Player</t>
         </is>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="13">
         <f>B36/$G$4</f>
         <v/>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="13">
         <f>C36/$G$4</f>
         <v/>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="13">
         <f>B40-C40</f>
         <v/>
       </c>
-      <c r="E40" s="10" t="inlineStr"/>
-      <c r="F40" s="13" t="inlineStr"/>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr"/>
+      <c r="F40" s="15" t="inlineStr"/>
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>Total team cost divided by roster count</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Team Fundraising &amp; Sponsorship Raised Per Player</t>
         </is>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="13">
         <f>(B14+B15)/$G$4</f>
         <v/>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="13">
         <f>(C14+C15)/$G$4</f>
         <v/>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="13">
         <f>C41-B41</f>
         <v/>
       </c>
-      <c r="E41" s="10" t="inlineStr"/>
-      <c r="F41" s="13" t="inlineStr"/>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr"/>
+      <c r="F41" s="15" t="inlineStr"/>
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Subsidized through team sponsors &amp; events</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>Net Parent Out-of-Pocket Cost Per Player</t>
         </is>
       </c>
-      <c r="B42" s="23">
+      <c r="B42" s="25">
         <f>B16/$G$4</f>
         <v/>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="25">
         <f>C16/$G$4</f>
         <v/>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="25">
         <f>B42-C42</f>
         <v/>
       </c>
-      <c r="E42" s="22" t="inlineStr"/>
-      <c r="F42" s="24" t="inlineStr"/>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr"/>
+      <c r="F42" s="26" t="inlineStr"/>
+      <c r="G42" s="24" t="inlineStr">
         <is>
           <t>Actual parent fee required per family</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>4.0 EXECUTIVE GOVERNANCE &amp; SUBMISSION CHECKLIST</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="25" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>Milestone 1: Preliminary Budget presented to Parents &amp; approved (&gt;75% majority vote)</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>October 30, 2026</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>Manager &amp; Treasurer</t>
         </is>
       </c>
-      <c r="G46" s="24" t="inlineStr">
+      <c r="G46" s="26" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="25" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>Milestone 2: Preliminary Budget submitted to VP Finance (vpfinance@trurominorhockey.ca)</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E47" s="26" t="inlineStr">
         <is>
           <t>October 30, 2026</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>VP Finance (Joe Zappia)</t>
         </is>
       </c>
-      <c r="G47" s="24" t="inlineStr">
+      <c r="G47" s="26" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="25" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>Milestone 3: Mid-Season Financial Statement shared with Parent Group</t>
         </is>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>December 31, 2026</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>Parent Group</t>
         </is>
       </c>
-      <c r="G48" s="24" t="inlineStr">
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="25" t="inlineStr">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>Milestone 4: Interim Financial Statement submitted to VP Finance</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>January 15, 2027</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="F49" s="15" t="inlineStr">
         <is>
           <t>VP Finance (Joe Zappia)</t>
         </is>
       </c>
-      <c r="G49" s="24" t="inlineStr">
+      <c r="G49" s="26" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>Milestone 5: Final Year-End Budget &amp; Reconciliation submitted to VP Finance</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>March 31, 2027</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>VP Finance (Joe Zappia)</t>
         </is>
       </c>
-      <c r="G50" s="24" t="inlineStr">
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="inlineStr">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>Milestone 6: Final Financial Statement &amp; Jersey Deposit refunds distributed to Parents</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>April 15, 2027</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>Parent Group</t>
         </is>
       </c>
-      <c r="G51" s="24" t="inlineStr">
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A8:G10"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1586,939 +1655,941 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>1.0 SPONSORSHIPS &amp; LOCAL BUSINESS ADVERTISING</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Sponsor / Business Name</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Sponsorship Level</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Contact Person</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Actual Received ($)</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Receipt Issued?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>[Major Team Sponsor - e.g. Local Business]</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Major ($1,000+)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>[Gold Banner Sponsor 1]</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Gold ($500)</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>[Gold Banner Sponsor 2]</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Gold ($500)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>[Silver Banner Sponsor 1]</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Silver ($250)</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>[Silver Banner Sponsor 2]</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Silver ($250)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>[Silver Banner Sponsor 3]</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Silver ($250)</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>[Bronze Banner Sponsor 1]</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Bronze ($100)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>[Bronze Banner Sponsor 2]</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Bronze ($100)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>[Contact Name]</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>[Cheque / E-transfer]</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL: SPONSORSHIPS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="15">
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="17">
         <f>SUM(E6:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="17">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="14" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2.0 TEAM FUNDRAISING INITIATIVES</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Fundraiser Name / Description</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Lead Coordinator</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Actual Net ($)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Variance ($)</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Status / Notes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>[Team Bottle Drive - Fall]</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>[Oct 2026]</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>[Parent Volunteer]</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11">
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13">
         <f>E18-D18</f>
         <v/>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>[50/50 Raffle - e.g. Pot O' Gold]</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>[Nov 2026]</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>[Treasurer]</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="13" t="n">
         <v>1500</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="11">
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13">
         <f>E19-D19</f>
         <v/>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>[Ticket Draw / Grand In Your Hand]</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>[Dec 2026]</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>[Manager]</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="E20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="11">
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
         <f>E20-D20</f>
         <v/>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>[Square Board / Silent Auction]</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>[Feb 2027]</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>[Parent Committee]</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="11">
+      <c r="E21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
         <f>E21-D21</f>
         <v/>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>[Optional Fundraiser 5]</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>[TBD]</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>[Volunteer]</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="11">
+      <c r="D22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
         <f>E22-D22</f>
         <v/>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL: FUNDRAISING</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15">
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="17">
         <f>SUM(D18:D22)</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="17">
         <f>SUM(E18:E22)</f>
         <v/>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="17">
         <f>E23-D23</f>
         <v/>
       </c>
-      <c r="G23" s="14" t="n"/>
+      <c r="G23" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>3.0 PARENT CONTRIBUTIONS &amp; TEAM FEES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Fee Description</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Per Player ($)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Roster Size</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Projected Total ($)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Actual Collected ($)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Variance ($)</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Due Date / Installment</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Rep Fee Contribution - Installment 1 (Nov)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
-        <v>226.47</v>
-      </c>
-      <c r="C27" s="13">
+      <c r="B27" s="13">
+        <f>ROUND(Expenses!E6/'Budget Summary'!$G$4, 2)</f>
+        <v/>
+      </c>
+      <c r="C27" s="15">
         <f>'Budget Summary'!$G$4</f>
         <v/>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="13">
         <f>B27*C27</f>
         <v/>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="11">
+      <c r="E27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
         <f>E27-D27</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>November 15, 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Rep Fee Contribution - Installment 2 (Jan)</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
-        <v>226.47</v>
-      </c>
-      <c r="C28" s="13">
+      <c r="B28" s="13">
+        <f>ROUND(Expenses!E7/'Budget Summary'!$G$4, 2)</f>
+        <v/>
+      </c>
+      <c r="C28" s="15">
         <f>'Budget Summary'!$G$4</f>
         <v/>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="13">
         <f>B28*C28</f>
         <v/>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="11">
+      <c r="E28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
         <f>E28-D28</f>
         <v/>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>January 31, 2027</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Team Operational Cash Call (Apparel / Extras)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="15">
         <f>'Budget Summary'!$G$4</f>
         <v/>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="13">
         <f>B29*C29</f>
         <v/>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="11">
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
         <f>E29-D29</f>
         <v/>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>December 1, 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Optional Tournament / Extra Ice Cash Call</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="13">
+      <c r="B30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="15">
         <f>'Budget Summary'!$G$4</f>
         <v/>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="13">
         <f>B30*C30</f>
         <v/>
       </c>
-      <c r="E30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="11">
+      <c r="E30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13">
         <f>E30-D30</f>
         <v/>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>As needed</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL: PARENT CONTRIBUTIONS</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15">
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="17">
         <f>SUM(D27:D30)</f>
         <v/>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="17">
         <f>SUM(E27:E30)</f>
         <v/>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="17">
         <f>E33-D33</f>
         <v/>
       </c>
-      <c r="G33" s="14" t="n"/>
+      <c r="G33" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>4.0 PARENT JERSEY DEPOSITS (HELD IN TRUST)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Deposit Type</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Deposit / Player</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Roster Size</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Projected Total ($)</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Actual Collected ($)</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>Policy Rule</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Rep Team Jersey Deposit ($150 / player)</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="15">
         <f>'Budget Summary'!$G$4</f>
         <v/>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="13">
         <f>B37*C37</f>
         <v/>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="E37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>Post-dated cheque / E-transfer</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>Mandatory $150 Rep / $50 House</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Uncashed Cheques Held in Safe Keeping</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="13">
+      <c r="B38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="15">
         <f>'Budget Summary'!$G$4</f>
         <v/>
       </c>
-      <c r="D38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="D38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>Cheques dated May 15, 2027</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>Returned or destroyed upon jersey return</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL: JERSEY DEPOSITS HELD</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n"/>
-      <c r="C41" s="14" t="n"/>
-      <c r="D41" s="15">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="17">
         <f>D37+D38</f>
         <v/>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="17">
         <f>E37+E38</f>
         <v/>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="17">
         <f>E41-D41</f>
         <v/>
       </c>
-      <c r="G41" s="14" t="n"/>
+      <c r="G41" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>5.0 BANK INTEREST &amp; MISCELLANEOUS REVENUE</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>Mosaik Credit Union Account Interest</t>
         </is>
       </c>
-      <c r="D44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="27" t="inlineStr">
+      <c r="D44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="29" t="inlineStr">
         <is>
           <t>Credit Union operating account interest</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL: MISCELLANEOUS REVENUE</t>
         </is>
       </c>
-      <c r="B47" s="14" t="n"/>
-      <c r="C47" s="14" t="n"/>
-      <c r="D47" s="15">
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="17">
         <f>D44</f>
         <v/>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="17">
         <f>E44</f>
         <v/>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="17">
         <f>E47-D47</f>
         <v/>
       </c>
-      <c r="G47" s="14" t="n"/>
+      <c r="G47" s="16" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="28" t="inlineStr">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>TOTAL TEAM REVENUE (ALL 5 CATEGORIES)</t>
         </is>
       </c>
-      <c r="B49" s="28" t="n"/>
-      <c r="C49" s="28" t="n"/>
-      <c r="D49" s="29">
+      <c r="B49" s="30" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31">
         <f>E14+D23+D33+D41+D47</f>
         <v/>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="31">
         <f>F14+E23+E33+E41+E47</f>
         <v/>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="31">
         <f>E49-D49</f>
         <v/>
       </c>
-      <c r="G49" s="28">
+      <c r="G49" s="30">
         <f>IF(F49&gt;=0,"Surplus / Target Met","Pending")</f>
         <v/>
       </c>
@@ -2571,1376 +2642,1376 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>1.0 TAMHA ASSOCIATION &amp; LEAGUE FEES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Fee Description</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Payment Due Date</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Actual Paid ($)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Notes / Invoices</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>TAMHA Rep Fees - Installment 1 (50%)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Nov 15, 2026</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Cheque / E-transfer</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>3850</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Official association invoice</t>
+      <c r="E6" s="13" t="n">
+        <v>4750</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Official association invoice (includes jersey fund)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TAMHA Rep Fees - Installment 2 (50%)</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Jan 31, 2027</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Cheque / E-transfer</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>3850</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Official association invoice</t>
+      <c r="E7" s="13" t="n">
+        <v>4750</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Official association invoice (includes jersey fund)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>TAMHA Mandatory Sweater / Jersey Fund</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Nov 15, 2026</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Included in Rep Fee</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Included in the $9,500 Rep Fee total (no separate payment required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>HNS / Conference League Scheduling Fees</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Nov 1, 2026</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>E-transfer</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Populated by manager if applicable to league</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>League / Regional Playoff Assessment Fees</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Feb 15, 2027</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Cheque</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Populated by manager when assessed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: TAMHA &amp; LEAGUE FEES</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="17">
+        <f>SUM(E6:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>SUM(F6:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>2.0 TOURNAMENTS &amp; JAMBOREES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Tournament Name</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Tournament Dates</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Permit Status</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Projected ($)</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Actual Paid ($)</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Travel Permits</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Tournament 1: [Early Bird / Pre-Season Event]</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>[Host Town, NS]</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Sanctioned</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>850</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Early season tournament</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Tournament 2: [Holiday / Winter Invitational]</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>[Host Town, NS]</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Sanctioned</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Holiday event</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Tournament 3: [SEDMHA / March Tournament]</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Halifax / Dartmouth</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Sanctioned</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Major spring tournament</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Tournament 4: [Away / Travel Tournament]</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>[PEI / NB / Local]</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Sanctioned</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>850</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Travel permit required</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: TOURNAMENTS</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="17">
+        <f>SUM(E18:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="17">
+        <f>SUM(F18:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="17">
+        <f>E22-F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>3.0 EXTRA PRACTICE ICE &amp; GAME OFFICIALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Ice / Official Item</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Rate &amp; Quantity</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Facility / Venue</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Event Type</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Projected ($)</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Actual Paid ($)</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Invoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Additional Practice Ice (Full Ice)</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>6 Hours @ $165/hr</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Local Rink / RECC</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Pre-Season / Practice</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>990</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Extra team development ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Exhibition Game Ice Rental</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>2 Games @ $258/game</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Home Rink</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Exhibition</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>516</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Home exhibition game slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Referee &amp; Linesmen Official Fees</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>2 Games @ $90/game</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>HNS Certified Officials</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Exhibition</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>180</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Cash payout for officials</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Timekeeper &amp; Scorekeeper Fees</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>2 Games @ $30/game</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Timekeeper Association</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Exhibition</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Clock / game sheet operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: EXTRA ICE &amp; OFFICIALS</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="17">
+        <f>SUM(E28:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="17">
+        <f>SUM(F28:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="17">
+        <f>E32-F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>4.0 TEAM APPAREL, GEAR &amp; ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Quantity &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Vendor / Supplier</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Projected ($)</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Actual Paid ($)</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Receipts</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Practice Jerseys (Home &amp; Away Colors)</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>17 Sets @ $32.35</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Apparel Vendor</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Team Property</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="n">
         <v>550</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>$550 mandatory contribution per team</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>HNS / Conference League Scheduling Fees</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Nov 1, 2026</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>E-transfer</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>If applicable</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>175</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>Covered or invoiced separately</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>League / Regional Playoff Assessment Fees</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Feb 15, 2027</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Cheque</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Playoff ice / officials assessment</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: TAMHA &amp; LEAGUE FEES</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="15">
-        <f>SUM(E6:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="15">
-        <f>SUM(F6:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="15">
-        <f>E11-F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>2.0 TOURNAMENTS &amp; JAMBOREES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Tournament Name</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Tournament Dates</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Permit Status</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="F37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Kept by team / passed down</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Sponsor Display Banner (Printed)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Arena Display Banner</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Local Print Shop</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Sponsor Value</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>Displays sponsor logos at arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Sponsor Bars / Player Name Bars &amp; Sewing</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>17 Players</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Sewing Specialist</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Player Apparel</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>Custom name bars sewn on game jerseys</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Team Game Socks (Home &amp; Away)</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>17 Players @ 2 pairs</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Equipment Manager</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Mandatory Gear</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>680</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Official Truro Bearcats colors</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Team First Aid Kit &amp; Safety Supplies</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Full Season Kit</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Local Pharmacy / Sport</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Safety Person</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Required for every team bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Practice Pucks, Cones, Whiteboard</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Puck bag &amp; coaching items</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Sporting Goods</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Coaching Staff</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Team practice equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: APPAREL &amp; TEAM ITEMS</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="17">
+        <f>SUM(E37:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>SUM(F37:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>E43-F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>5.0 TEAM ACTIVITIES &amp; PLAYER EVENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Activity / Event Name</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Date / Frequency</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Location / Details</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Participants</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Actual Paid ($)</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Notes / Travel Permits</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Tournament 1: [Early Bird / Pre-Season Event]</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>[Host Town, NS]</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Sanctioned</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>850</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Early season tournament</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Tournament 2: [Holiday / Winter Invitational]</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Receipts</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Holiday / Christmas Family Team Party</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>Dec 2026</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>[Host Town, NS]</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Sanctioned</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Holiday event</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Tournament 3: [SEDMHA / March Tournament]</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>Mar 2027</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Halifax / Dartmouth</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Sanctioned</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Major spring tournament</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Tournament 4: [Away / Travel Tournament]</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Mar 2027</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>[PEI / NB / Local]</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Sanctioned</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>850</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Travel permit required</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: TOURNAMENTS</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="15">
-        <f>SUM(E18:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="15">
-        <f>SUM(F18:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="15">
-        <f>E22-F22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>3.0 EXTRA PRACTICE ICE &amp; GAME OFFICIALS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Ice / Official Item</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Rate &amp; Quantity</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Facility / Venue</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Local Venue / Rink</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>All Families</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Food, activities, gifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Year-End Team Party &amp; Banquet</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Local Restaurant / Hall</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>All Families</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Awards, meal, celebration</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Team Away Game Snacks &amp; Nutrition</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Full Season</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Grocery / Wholesale</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Player Health</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>Fruit, granola bars, electrolytes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Coaching Staff Appreciation Gifts</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Head Coach &amp; Bench Staff</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Local Retailer</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Volunteer Recognition</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>End-of-year volunteer gifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: TEAM ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="17">
+        <f>SUM(E47:E50)</f>
+        <v/>
+      </c>
+      <c r="F51" s="17">
+        <f>SUM(F47:F50)</f>
+        <v/>
+      </c>
+      <c r="G51" s="17">
+        <f>E51-F51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>6.0 OPERATING COSTS, BANKING &amp; CONTINGENCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Operational Item</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Calculation Basis</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Actual Paid ($)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Notes / Invoices</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Additional Practice Ice (Full Ice)</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>6 Hours @ $165/hr</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Local Rink / RECC</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Pre-Season / Practice</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>990</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Extra team development ice</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Exhibition Game Ice Rental</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>2 Games @ $258/game</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Home Rink</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Exhibition</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>516</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Home exhibition game slots</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Referee &amp; Linesmen Official Fees</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>2 Games @ $90/game</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>HNS Certified Officials</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>Exhibition</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Cash payout for officials</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Timekeeper &amp; Scorekeeper Fees</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>2 Games @ $30/game</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Timekeeper Association</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Exhibition</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>Clock / game sheet operator</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: EXTRA ICE &amp; OFFICIALS</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="15">
-        <f>SUM(E28:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="15">
-        <f>SUM(F28:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="15">
-        <f>E32-F32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>4.0 TEAM APPAREL, GEAR &amp; ITEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Item Description</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Quantity &amp; Pricing</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Vendor / Supplier</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Mosaik Credit Union Monthly Service Fees</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>7 Months @ $15/mo</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Mosaik Truro Branch</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Bank Maintenance</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>$15/month commercial account</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Banking Supplies (Chequebook, Deposit Slips)</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>1 Order</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>Mosaik Truro</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>Cheque printing fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Emergency Contingency Fund (Unexpected Ice/Playoffs)</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Season Buffer</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Held in Account</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>Safety margin for unexpected costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>SUBTOTAL: OPERATING &amp; BANKING</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="n"/>
+      <c r="C59" s="16" t="n"/>
+      <c r="D59" s="16" t="n"/>
+      <c r="E59" s="17">
+        <f>SUM(E56:E58)</f>
+        <v/>
+      </c>
+      <c r="F59" s="17">
+        <f>SUM(F56:F58)</f>
+        <v/>
+      </c>
+      <c r="G59" s="17">
+        <f>E59-F59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>7.0 PARENT JERSEY DEPOSIT REFUNDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>Refund Description</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Quantity &amp; Basis</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Target Date</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>Projected ($)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Actual Paid ($)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Notes / Receipts</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Practice Jerseys (Home &amp; Away Colors)</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>17 Sets @ $32.35</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>Apparel Vendor</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>Team Property</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>550</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>Kept by team / passed down</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>Sponsor Display Banner (Printed)</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Arena Display Banner</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>Local Print Shop</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>Sponsor Value</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Displays sponsor logos at arena</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Sponsor Bars / Player Name Bars &amp; Sewing</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>17 Players</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>Sewing Specialist</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Player Apparel</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>Custom name bars sewn on game jerseys</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Team Game Socks (Home &amp; Away)</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>17 Players @ 2 pairs</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>Equipment Manager</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory Gear</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>680</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>Official Truro Bearcats colors</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Team First Aid Kit &amp; Safety Supplies</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>Full Season Kit</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>Local Pharmacy / Sport</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>Safety Person</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>Required for every team bench</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Practice Pucks, Cones, Whiteboard</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>Puck bag &amp; coaching items</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>Sporting Goods</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>Coaching Staff</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>Team practice equipment</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: APPAREL &amp; TEAM ITEMS</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="n"/>
-      <c r="C43" s="14" t="n"/>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="15">
-        <f>SUM(E37:E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="15">
-        <f>SUM(F37:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="15">
-        <f>E43-F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
-        <is>
-          <t>5.0 TEAM ACTIVITIES &amp; PLAYER EVENTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Activity / Event Name</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Date / Frequency</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Location / Details</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>Participants</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>Projected ($)</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Actual Paid ($)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>Notes / Receipts</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Holiday / Christmas Family Team Party</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>Local Venue / Rink</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>All Families</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="F47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t>Food, activities, gifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Year-End Team Party &amp; Banquet</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>Local Restaurant / Hall</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>All Families</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>Awards, meal, celebration</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>Team Away Game Snacks &amp; Nutrition</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Full Season</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>Grocery / Wholesale</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>Player Health</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>Fruit, granola bars, electrolytes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>Coaching Staff Appreciation Gifts</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>Head Coach &amp; Bench Staff</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>Local Retailer</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>Volunteer Recognition</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="F50" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>End-of-year volunteer gifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: TEAM ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="n"/>
-      <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="15">
-        <f>SUM(E47:E50)</f>
-        <v/>
-      </c>
-      <c r="F51" s="15">
-        <f>SUM(F47:F50)</f>
-        <v/>
-      </c>
-      <c r="G51" s="15">
-        <f>E51-F51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>6.0 OPERATING COSTS, BANKING &amp; CONTINGENCY</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Operational Item</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Calculation Basis</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>Projected ($)</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Actual Paid ($)</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Notes / Verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Mosaik Credit Union Monthly Service Fees</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>7 Months @ $15/mo</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>Mosaik Truro Branch</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Bank Maintenance</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="F56" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>$15/month commercial account</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Banking Supplies (Chequebook, Deposit Slips)</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>1 Order</t>
-        </is>
-      </c>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>Mosaik Truro</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="F57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>Cheque printing fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Emergency Contingency Fund (Unexpected Ice/Playoffs)</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>Season Buffer</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>Held in Account</t>
-        </is>
-      </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>Buffer</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="F58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>Safety margin for unexpected costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>SUBTOTAL: OPERATING &amp; BANKING</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="n"/>
-      <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="15">
-        <f>SUM(E56:E58)</f>
-        <v/>
-      </c>
-      <c r="F59" s="15">
-        <f>SUM(F56:F58)</f>
-        <v/>
-      </c>
-      <c r="G59" s="15">
-        <f>E59-F59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>7.0 PARENT JERSEY DEPOSIT REFUNDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Refund Description</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>Quantity &amp; Basis</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>Target Date</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>Projected ($)</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>Actual Paid ($)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr">
         <is>
           <t>Policy Rule</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>Return of Parent Jersey Deposits (100% Refund)</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>17 Players @ $150</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>End of Season (Apr 2027)</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>Trust Return</t>
         </is>
       </c>
-      <c r="E64" s="11" t="n">
+      <c r="E64" s="13" t="n">
         <v>2550</v>
       </c>
-      <c r="F64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="F64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>Refunded in full upon jersey return</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL: JERSEY DEPOSIT REFUNDS</t>
         </is>
       </c>
-      <c r="B65" s="14" t="n"/>
-      <c r="C65" s="14" t="n"/>
-      <c r="D65" s="14" t="n"/>
-      <c r="E65" s="15">
+      <c r="B65" s="16" t="n"/>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="17">
         <f>SUM(E64:E64)</f>
         <v/>
       </c>
-      <c r="F65" s="15">
+      <c r="F65" s="17">
         <f>SUM(F64:F64)</f>
         <v/>
       </c>
-      <c r="G65" s="15">
+      <c r="G65" s="17">
         <f>E65-F65</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+      <c r="A68" s="32" t="inlineStr">
         <is>
           <t>TOTAL TEAM EXPENSES (ALL 7 CATEGORIES)</t>
         </is>
       </c>
-      <c r="B68" s="30" t="n"/>
-      <c r="C68" s="30" t="n"/>
-      <c r="D68" s="30" t="n"/>
-      <c r="E68" s="31">
+      <c r="B68" s="32" t="n"/>
+      <c r="C68" s="32" t="n"/>
+      <c r="D68" s="32" t="n"/>
+      <c r="E68" s="33">
         <f>E11+E22+E32+E43+E51+E59+E65</f>
         <v/>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="33">
         <f>F11+F22+F32+F43+F51+F59+F65</f>
         <v/>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="33">
         <f>E68-F68</f>
         <v/>
       </c>
@@ -3993,13 +4064,25 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>ℹ️ OPTIONAL TOOL: This reconciliation ledger is provided for team convenience and is NOT required for your official TAMHA budget submission.</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Team Name:</t>
         </is>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="27">
         <f>'Budget Summary'!$B$4</f>
         <v/>
       </c>
@@ -4008,7 +4091,7 @@
           <t>Mosaik Account #:</t>
         </is>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="27">
         <f>'Budget Summary'!$B$6</f>
         <v/>
       </c>
@@ -4019,7 +4102,7 @@
           <t>Statement Date:</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>[Enter Statement Date - e.g. Oct 31, 2026]</t>
         </is>
@@ -4029,358 +4112,358 @@
           <t>Reconciled By:</t>
         </is>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="27">
         <f>'Budget Summary'!$G$5</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>1. Ending Balance per Mosaik Bank Statement</t>
         </is>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2. ADD: Outstanding Deposits (Recorded in ledger, not yet cleared on bank statement)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Deposit Description</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Date Received</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Payer / Source</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>[Deposit 1 Description]</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>[Date]</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>[Source / Payer]</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>[Method]</t>
         </is>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>[Pending clearance]</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>[Deposit 2 Description]</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>[Date]</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>[Source / Payer]</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>[Method]</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>[Pending clearance]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>[Deposit 3 Description]</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>[Date]</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>[Source / Payer]</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>[Method]</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="E13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>[Pending clearance]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr"/>
-      <c r="B14" s="13" t="inlineStr"/>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr"/>
-      <c r="E14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="12" t="inlineStr"/>
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="13" t="inlineStr"/>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr"/>
-      <c r="E15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr"/>
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="12" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>TOTAL OUTSTANDING DEPOSITS</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="15">
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="17">
         <f>SUM(E11:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="14" t="n"/>
+      <c r="F16" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>3. LESS: Outstanding Withdrawals &amp; Cheques (Issued in ledger, not yet cashed)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Cheque # / Transaction</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Date Issued</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Payee / Vendor</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>[Cheque #101]</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>[Date]</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>[Payee / Vendor]</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>[Description / Purpose]</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>Issued, not yet cashed</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>[Cheque #102]</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>[Date]</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>[Payee / Vendor]</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>[Description / Purpose]</t>
         </is>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="E21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>Issued, not yet cashed</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>[Cheque #103]</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>[Date]</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>[Payee / Vendor]</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>[Description / Purpose]</t>
         </is>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="E22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>Issued, not yet cashed</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr"/>
-      <c r="B23" s="13" t="inlineStr"/>
-      <c r="C23" s="10" t="inlineStr"/>
-      <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr"/>
+      <c r="B23" s="15" t="inlineStr"/>
+      <c r="C23" s="12" t="inlineStr"/>
+      <c r="D23" s="12" t="inlineStr"/>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr"/>
-      <c r="B24" s="13" t="inlineStr"/>
-      <c r="C24" s="10" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13" t="inlineStr"/>
+      <c r="A24" s="15" t="inlineStr"/>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="12" t="inlineStr"/>
+      <c r="D24" s="12" t="inlineStr"/>
+      <c r="E24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr"/>
-      <c r="B25" s="13" t="inlineStr"/>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13" t="inlineStr"/>
+      <c r="A25" s="15" t="inlineStr"/>
+      <c r="B25" s="15" t="inlineStr"/>
+      <c r="C25" s="12" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr"/>
+      <c r="E25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>TOTAL OUTSTANDING WITHDRAWALS</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="15">
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="17">
         <f>SUM(E20:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="14" t="n"/>
+      <c r="F26" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -4391,7 +4474,7 @@
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
-      <c r="E28" s="34">
+      <c r="E28" s="37">
         <f>E7+E16-E26</f>
         <v/>
       </c>
@@ -4406,32 +4489,32 @@
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
-      <c r="E29" s="34">
+      <c r="E29" s="37">
         <f>'Budget Summary'!C21-'Budget Summary'!C36</f>
         <v/>
       </c>
       <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>6. UNRECONCILED VARIANCE / DIFFERENCE (Must equal $0.00)</t>
         </is>
       </c>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="29">
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="31">
         <f>E28-E29</f>
         <v/>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="38">
         <f>IF(ROUND(E30,2)=0,"✅ BALANCED - PERFECT RECONCILIATION","⚠️ OUT OF BALANCE")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A26:D26"/>
@@ -4441,6 +4524,7 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4453,7 +4537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4483,905 +4567,1058 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>ℹ️ OPTIONAL TOOL: This roster and fee ledger is provided for team tracking and is NOT required for your official TAMHA budget submission.</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Jersey #</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Player Legal Name</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Parent / Guardian Contact</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Parent Email</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Jersey Deposit ($150)</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Rep Fee Install. 1 ($226.47)</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Rep Fee Install. 2 ($226.47)</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Rep Fee Installment 1</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Rep Fee Installment 2</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Team Fee / Cash Call ($100)</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Total Paid ($)</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Balance Due ($)</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Jersey Returned &amp; Deposit Cleared?</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>#01</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>[Player 01 Legal Name]</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 01]</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>[parent01@example.com]</t>
         </is>
       </c>
-      <c r="E5" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="36">
+      <c r="E5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="39">
         <f>SUM(E5:H5)</f>
         <v/>
       </c>
-      <c r="J5" s="36">
-        <f>(150+226.47+226.47+100)-I5</f>
-        <v/>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="J5" s="39">
+        <f>IF(B5="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>#02</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>[Player 02 Legal Name]</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 02]</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>[parent02@example.com]</t>
         </is>
       </c>
-      <c r="E6" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="36">
+      <c r="E6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="39">
         <f>SUM(E6:H6)</f>
         <v/>
       </c>
-      <c r="J6" s="36">
-        <f>(150+226.47+226.47+100)-I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="J6" s="39">
+        <f>IF(B6="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>#03</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>[Player 03 Legal Name]</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 03]</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>[parent03@example.com]</t>
         </is>
       </c>
-      <c r="E7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="36">
+      <c r="E7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="39">
         <f>SUM(E7:H7)</f>
         <v/>
       </c>
-      <c r="J7" s="36">
-        <f>(150+226.47+226.47+100)-I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="J7" s="39">
+        <f>IF(B7="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>#04</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>[Player 04 Legal Name]</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 04]</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>[parent04@example.com]</t>
         </is>
       </c>
-      <c r="E8" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="36">
+      <c r="E8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="39">
         <f>SUM(E8:H8)</f>
         <v/>
       </c>
-      <c r="J8" s="36">
-        <f>(150+226.47+226.47+100)-I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="J8" s="39">
+        <f>IF(B8="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>#05</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>[Player 05 Legal Name]</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 05]</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>[parent05@example.com]</t>
         </is>
       </c>
-      <c r="E9" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="36">
+      <c r="E9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="39">
         <f>SUM(E9:H9)</f>
         <v/>
       </c>
-      <c r="J9" s="36">
-        <f>(150+226.47+226.47+100)-I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="J9" s="39">
+        <f>IF(B9="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>#06</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>[Player 06 Legal Name]</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 06]</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>[parent06@example.com]</t>
         </is>
       </c>
-      <c r="E10" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="36">
+      <c r="E10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="39">
         <f>SUM(E10:H10)</f>
         <v/>
       </c>
-      <c r="J10" s="36">
-        <f>(150+226.47+226.47+100)-I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="J10" s="39">
+        <f>IF(B10="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>#07</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>[Player 07 Legal Name]</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 07]</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>[parent07@example.com]</t>
         </is>
       </c>
-      <c r="E11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="36">
+      <c r="E11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="39">
         <f>SUM(E11:H11)</f>
         <v/>
       </c>
-      <c r="J11" s="36">
-        <f>(150+226.47+226.47+100)-I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="J11" s="39">
+        <f>IF(B11="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>#08</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>[Player 08 Legal Name]</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 08]</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>[parent08@example.com]</t>
         </is>
       </c>
-      <c r="E12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="36">
+      <c r="E12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="39">
         <f>SUM(E12:H12)</f>
         <v/>
       </c>
-      <c r="J12" s="36">
-        <f>(150+226.47+226.47+100)-I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="13" t="inlineStr">
+      <c r="J12" s="39">
+        <f>IF(B12="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>#09</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>[Player 09 Legal Name]</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 09]</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>[parent09@example.com]</t>
         </is>
       </c>
-      <c r="E13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="36">
+      <c r="E13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="39">
         <f>SUM(E13:H13)</f>
         <v/>
       </c>
-      <c r="J13" s="36">
-        <f>(150+226.47+226.47+100)-I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="J13" s="39">
+        <f>IF(B13="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>[Player 10 Legal Name]</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 10]</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>[parent10@example.com]</t>
         </is>
       </c>
-      <c r="E14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="36">
+      <c r="E14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="39">
         <f>SUM(E14:H14)</f>
         <v/>
       </c>
-      <c r="J14" s="36">
-        <f>(150+226.47+226.47+100)-I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="J14" s="39">
+        <f>IF(B14="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>[Player 11 Legal Name]</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 11]</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>[parent11@example.com]</t>
         </is>
       </c>
-      <c r="E15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="36">
+      <c r="E15" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="39">
         <f>SUM(E15:H15)</f>
         <v/>
       </c>
-      <c r="J15" s="36">
-        <f>(150+226.47+226.47+100)-I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="J15" s="39">
+        <f>IF(B15="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>[Player 12 Legal Name]</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 12]</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>[parent12@example.com]</t>
         </is>
       </c>
-      <c r="E16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
+      <c r="E16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="39">
         <f>SUM(E16:H16)</f>
         <v/>
       </c>
-      <c r="J16" s="36">
-        <f>(150+226.47+226.47+100)-I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="J16" s="39">
+        <f>IF(B16="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>[Player 13 Legal Name]</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 13]</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>[parent13@example.com]</t>
         </is>
       </c>
-      <c r="E17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
+      <c r="E17" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="39">
         <f>SUM(E17:H17)</f>
         <v/>
       </c>
-      <c r="J17" s="36">
-        <f>(150+226.47+226.47+100)-I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="J17" s="39">
+        <f>IF(B17="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>[Player 14 Legal Name]</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 14]</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>[parent14@example.com]</t>
         </is>
       </c>
-      <c r="E18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="36">
+      <c r="E18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="39">
         <f>SUM(E18:H18)</f>
         <v/>
       </c>
-      <c r="J18" s="36">
-        <f>(150+226.47+226.47+100)-I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="J18" s="39">
+        <f>IF(B18="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>[Player 15 Legal Name]</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 15]</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>[parent15@example.com]</t>
         </is>
       </c>
-      <c r="E19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="36">
+      <c r="E19" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="39">
         <f>SUM(E19:H19)</f>
         <v/>
       </c>
-      <c r="J19" s="36">
-        <f>(150+226.47+226.47+100)-I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="J19" s="39">
+        <f>IF(B19="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>#16</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>[Player 16 Legal Name]</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 16]</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>[parent16@example.com]</t>
         </is>
       </c>
-      <c r="E20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="36">
+      <c r="E20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="39">
         <f>SUM(E20:H20)</f>
         <v/>
       </c>
-      <c r="J20" s="36">
-        <f>(150+226.47+226.47+100)-I20</f>
-        <v/>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="J20" s="39">
+        <f>IF(B20="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>[Player 17 Legal Name]</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>[Parent / Guardian of Player 17]</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>[parent17@example.com]</t>
         </is>
       </c>
-      <c r="E21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="36">
+      <c r="E21" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="39">
         <f>SUM(E21:H21)</f>
         <v/>
       </c>
-      <c r="J21" s="36">
-        <f>(150+226.47+226.47+100)-I21</f>
-        <v/>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="J21" s="39">
+        <f>IF(B21="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="inlineStr"/>
-      <c r="B22" s="38" t="inlineStr">
-        <is>
-          <t>TOTALS: ALL 17 PLAYERS</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr"/>
-      <c r="D22" s="37" t="inlineStr"/>
-      <c r="E22" s="15">
-        <f>SUM(E5:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="15">
-        <f>SUM(F5:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="15">
-        <f>SUM(G5:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="15">
-        <f>SUM(H5:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="15">
-        <f>SUM(I5:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="15">
-        <f>SUM(J5:J21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="39" t="inlineStr">
-        <is>
-          <t>17 Players Accounted For</t>
-        </is>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>#18</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="39">
+        <f>IF(B22="","",SUM(E22:H22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="39">
+        <f>IF(B22="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="15">
+        <f>IF(B22="","","Pending")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>#19</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="39">
+        <f>IF(B23="","",SUM(E23:H23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="39">
+        <f>IF(B23="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="15">
+        <f>IF(B23="","","Pending")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>#20</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="39">
+        <f>IF(B24="","",SUM(E24:H24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="39">
+        <f>IF(B24="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>IF(B24="","","Pending")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>#21</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="39">
+        <f>IF(B25="","",SUM(E25:H25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="39">
+        <f>IF(B25="","",(Income!$B$37+Income!$B$27+Income!$B$28+Income!$B$29)-I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="15">
+        <f>IF(B25="","","Pending")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr"/>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>TOTALS: ACTIVE ROSTER</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr"/>
+      <c r="D26" s="40" t="inlineStr"/>
+      <c r="E26" s="17">
+        <f>SUM(E5:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="17">
+        <f>SUM(F5:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="17">
+        <f>SUM(G5:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="17">
+        <f>SUM(H5:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="17">
+        <f>SUM(I5:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="17">
+        <f>SUM(J5:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="42">
+        <f>COUNTA(B5:B25) &amp; " Players Accounted For"</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
